--- a/Near Expiry iNVENTORY_.xlsx
+++ b/Near Expiry iNVENTORY_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/inventory_tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF101919-589C-204E-9854-505B131269D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8601E31-53C8-AB45-A87D-C7E14A2D47C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31960" yWindow="2020" windowWidth="30240" windowHeight="17440" xr2:uid="{1E79184A-48F2-C74D-A285-BE20DE170D2B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{1E79184A-48F2-C74D-A285-BE20DE170D2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Ageing Report" sheetId="1" r:id="rId1"/>
@@ -1765,7 +1765,7 @@
     <t>BNUNC074300626</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Days to LBD</t>
   </si>
 </sst>
 </file>
@@ -1876,87 +1876,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -30261,39 +30181,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="J642:M753">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J641">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M641">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K641">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L641">
+  <conditionalFormatting sqref="J2:M753">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
